--- a/research/traditional_assets/database/data/singapore/singapore_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_insurance_general.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-3.165289256198347</v>
+        <v>-1.937644341801386</v>
       </c>
       <c r="H2">
-        <v>-3.165289256198347</v>
+        <v>-1.937644341801386</v>
       </c>
       <c r="I2">
-        <v>-3.181818181818182</v>
+        <v>-2.632794457274827</v>
       </c>
       <c r="J2">
-        <v>-3.181818181818182</v>
+        <v>-2.632794457274827</v>
       </c>
       <c r="K2">
-        <v>38.5</v>
+        <v>-1.85</v>
       </c>
       <c r="L2">
-        <v>31.81818181818182</v>
+        <v>-4.272517321016166</v>
       </c>
       <c r="M2">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>1.626442812172088</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.4025974025974026</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,82 +621,70 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
-        <v>15.5</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.52</v>
+        <v>1.47</v>
       </c>
       <c r="V2">
-        <v>0.2644281217208814</v>
+        <v>0.2653429602888087</v>
       </c>
       <c r="W2">
-        <v>6.053459119496855</v>
+        <v>-1.141975308641975</v>
       </c>
       <c r="X2">
-        <v>0.04484279534562632</v>
+        <v>0.07661521055702399</v>
       </c>
       <c r="Y2">
-        <v>6.008616324151228</v>
-      </c>
-      <c r="Z2">
-        <v>-1.957928802588996</v>
-      </c>
-      <c r="AA2">
-        <v>6.22977346278317</v>
+        <v>-1.218590519198999</v>
       </c>
       <c r="AB2">
-        <v>0.04395049969803429</v>
-      </c>
-      <c r="AC2">
-        <v>6.185822963085135</v>
+        <v>0.07502956267955349</v>
       </c>
       <c r="AD2">
-        <v>0.41</v>
+        <v>0.299</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.41</v>
+        <v>0.299</v>
       </c>
       <c r="AG2">
-        <v>-2.11</v>
+        <v>-1.171</v>
       </c>
       <c r="AH2">
-        <v>0.04124748490945674</v>
+        <v>0.05120739852714505</v>
       </c>
       <c r="AI2">
-        <v>0.2019704433497537</v>
+        <v>0.2168237853517041</v>
       </c>
       <c r="AJ2">
-        <v>-0.284366576819407</v>
+        <v>-0.2680247196154727</v>
       </c>
       <c r="AK2">
-        <v>4.306122448979593</v>
+        <v>12.86813186813187</v>
       </c>
       <c r="AL2">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AM2">
-        <v>0.002</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AN2">
-        <v>-0.1184971098265896</v>
+        <v>-0.3497076023391813</v>
       </c>
       <c r="AO2">
-        <v>-962.5</v>
+        <v>-126.6666666666667</v>
       </c>
       <c r="AP2">
-        <v>0.6098265895953757</v>
+        <v>1.369590643274854</v>
       </c>
       <c r="AQ2">
-        <v>-1925</v>
+        <v>-126.6666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -716,31 +704,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-3.165289256198347</v>
+        <v>-1.937644341801386</v>
       </c>
       <c r="H3">
-        <v>-3.165289256198347</v>
+        <v>-1.937644341801386</v>
       </c>
       <c r="I3">
-        <v>-3.181818181818182</v>
+        <v>-2.632794457274827</v>
       </c>
       <c r="J3">
-        <v>-3.181818181818182</v>
+        <v>-2.632794457274827</v>
       </c>
       <c r="K3">
-        <v>38.5</v>
+        <v>-1.85</v>
       </c>
       <c r="L3">
-        <v>31.81818181818182</v>
+        <v>-4.272517321016166</v>
       </c>
       <c r="M3">
-        <v>15.5</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>1.626442812172088</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.4025974025974026</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,82 +737,70 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>15.5</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>2.52</v>
+        <v>1.47</v>
       </c>
       <c r="V3">
-        <v>0.2644281217208814</v>
+        <v>0.2653429602888087</v>
       </c>
       <c r="W3">
-        <v>6.053459119496855</v>
+        <v>-1.141975308641975</v>
       </c>
       <c r="X3">
-        <v>0.04484279534562632</v>
+        <v>0.07661521055702399</v>
       </c>
       <c r="Y3">
-        <v>6.008616324151228</v>
-      </c>
-      <c r="Z3">
-        <v>-1.957928802588996</v>
-      </c>
-      <c r="AA3">
-        <v>6.22977346278317</v>
+        <v>-1.218590519198999</v>
       </c>
       <c r="AB3">
-        <v>0.04395049969803429</v>
-      </c>
-      <c r="AC3">
-        <v>6.185822963085135</v>
+        <v>0.07502956267955349</v>
       </c>
       <c r="AD3">
-        <v>0.41</v>
+        <v>0.299</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.41</v>
+        <v>0.299</v>
       </c>
       <c r="AG3">
-        <v>-2.11</v>
+        <v>-1.171</v>
       </c>
       <c r="AH3">
-        <v>0.04124748490945674</v>
+        <v>0.05120739852714505</v>
       </c>
       <c r="AI3">
-        <v>0.2019704433497537</v>
+        <v>0.2168237853517041</v>
       </c>
       <c r="AJ3">
-        <v>-0.284366576819407</v>
+        <v>-0.2680247196154727</v>
       </c>
       <c r="AK3">
-        <v>4.306122448979593</v>
+        <v>12.86813186813187</v>
       </c>
       <c r="AL3">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AM3">
-        <v>0.002</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AN3">
-        <v>-0.1184971098265896</v>
+        <v>-0.3497076023391813</v>
       </c>
       <c r="AO3">
-        <v>-962.5</v>
+        <v>-126.6666666666667</v>
       </c>
       <c r="AP3">
-        <v>0.6098265895953757</v>
+        <v>1.369590643274854</v>
       </c>
       <c r="AQ3">
-        <v>-1925</v>
+        <v>-126.6666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/singapore/singapore_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_insurance_general.xlsx
@@ -587,23 +587,26 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.539</v>
+      </c>
       <c r="G2">
-        <v>-1.937644341801386</v>
+        <v>-5.41304347826087</v>
       </c>
       <c r="H2">
-        <v>-1.937644341801386</v>
+        <v>-5.41304347826087</v>
       </c>
       <c r="I2">
-        <v>-2.632794457274827</v>
+        <v>-4.625</v>
       </c>
       <c r="J2">
-        <v>-2.632794457274827</v>
+        <v>-4.625</v>
       </c>
       <c r="K2">
-        <v>-1.85</v>
+        <v>-0.912</v>
       </c>
       <c r="L2">
-        <v>-4.272517321016166</v>
+        <v>-4.956521739130435</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,64 +630,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.47</v>
+        <v>0.802</v>
       </c>
       <c r="V2">
-        <v>0.2653429602888087</v>
+        <v>0.1995024875621891</v>
       </c>
       <c r="W2">
-        <v>-1.141975308641975</v>
+        <v>-0.8444444444444444</v>
       </c>
       <c r="X2">
-        <v>0.07661521055702399</v>
+        <v>0.0690064011881405</v>
       </c>
       <c r="Y2">
-        <v>-1.218590519198999</v>
+        <v>-0.9134508456325849</v>
       </c>
       <c r="AB2">
-        <v>0.07502956267955349</v>
+        <v>0.06748081229498945</v>
       </c>
       <c r="AD2">
-        <v>0.299</v>
+        <v>0.266</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.299</v>
+        <v>0.266</v>
       </c>
       <c r="AG2">
-        <v>-1.171</v>
+        <v>-0.536</v>
       </c>
       <c r="AH2">
-        <v>0.05120739852714505</v>
+        <v>0.06206252916472236</v>
       </c>
       <c r="AI2">
-        <v>0.2168237853517041</v>
+        <v>0.5683760683760684</v>
       </c>
       <c r="AJ2">
-        <v>-0.2680247196154727</v>
+        <v>-0.1538461538461539</v>
       </c>
       <c r="AK2">
-        <v>12.86813186813187</v>
+        <v>1.604790419161677</v>
       </c>
       <c r="AL2">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="AM2">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="AN2">
-        <v>-0.3497076023391813</v>
+        <v>-0.344559585492228</v>
       </c>
       <c r="AO2">
-        <v>-126.6666666666667</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="AP2">
-        <v>1.369590643274854</v>
+        <v>0.6943005181347151</v>
       </c>
       <c r="AQ2">
-        <v>-126.6666666666667</v>
+        <v>-141.8333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -703,23 +706,26 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.539</v>
+      </c>
       <c r="G3">
-        <v>-1.937644341801386</v>
+        <v>-5.41304347826087</v>
       </c>
       <c r="H3">
-        <v>-1.937644341801386</v>
+        <v>-5.41304347826087</v>
       </c>
       <c r="I3">
-        <v>-2.632794457274827</v>
+        <v>-4.625</v>
       </c>
       <c r="J3">
-        <v>-2.632794457274827</v>
+        <v>-4.625</v>
       </c>
       <c r="K3">
-        <v>-1.85</v>
+        <v>-0.912</v>
       </c>
       <c r="L3">
-        <v>-4.272517321016166</v>
+        <v>-4.956521739130435</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,64 +749,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.47</v>
+        <v>0.802</v>
       </c>
       <c r="V3">
-        <v>0.2653429602888087</v>
+        <v>0.1995024875621891</v>
       </c>
       <c r="W3">
-        <v>-1.141975308641975</v>
+        <v>-0.8444444444444444</v>
       </c>
       <c r="X3">
-        <v>0.07661521055702399</v>
+        <v>0.0690064011881405</v>
       </c>
       <c r="Y3">
-        <v>-1.218590519198999</v>
+        <v>-0.9134508456325849</v>
       </c>
       <c r="AB3">
-        <v>0.07502956267955349</v>
+        <v>0.06748081229498945</v>
       </c>
       <c r="AD3">
-        <v>0.299</v>
+        <v>0.266</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.299</v>
+        <v>0.266</v>
       </c>
       <c r="AG3">
-        <v>-1.171</v>
+        <v>-0.536</v>
       </c>
       <c r="AH3">
-        <v>0.05120739852714505</v>
+        <v>0.06206252916472236</v>
       </c>
       <c r="AI3">
-        <v>0.2168237853517041</v>
+        <v>0.5683760683760684</v>
       </c>
       <c r="AJ3">
-        <v>-0.2680247196154727</v>
+        <v>-0.1538461538461539</v>
       </c>
       <c r="AK3">
-        <v>12.86813186813187</v>
+        <v>1.604790419161677</v>
       </c>
       <c r="AL3">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="AM3">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="AN3">
-        <v>-0.3497076023391813</v>
+        <v>-0.344559585492228</v>
       </c>
       <c r="AO3">
-        <v>-126.6666666666667</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="AP3">
-        <v>1.369590643274854</v>
+        <v>0.6943005181347151</v>
       </c>
       <c r="AQ3">
-        <v>-126.6666666666667</v>
+        <v>-141.8333333333333</v>
       </c>
     </row>
   </sheetData>
